--- a/data/nzd0149/nzd0149.xlsx
+++ b/data/nzd0149/nzd0149.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H659"/>
+  <dimension ref="A1:H661"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20208,6 +20208,66 @@
         <v>374.32</v>
       </c>
       <c r="H659" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B660" t="n">
+        <v>365.06</v>
+      </c>
+      <c r="C660" t="n">
+        <v>369.29</v>
+      </c>
+      <c r="D660" t="n">
+        <v>368.08</v>
+      </c>
+      <c r="E660" t="n">
+        <v>365.01</v>
+      </c>
+      <c r="F660" t="n">
+        <v>369.01</v>
+      </c>
+      <c r="G660" t="n">
+        <v>372.06</v>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="B661" t="n">
+        <v>365.76</v>
+      </c>
+      <c r="C661" t="n">
+        <v>369.99</v>
+      </c>
+      <c r="D661" t="n">
+        <v>368.3</v>
+      </c>
+      <c r="E661" t="n">
+        <v>365.91</v>
+      </c>
+      <c r="F661" t="n">
+        <v>369.13</v>
+      </c>
+      <c r="G661" t="n">
+        <v>372.67</v>
+      </c>
+      <c r="H661" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -20224,7 +20284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B685"/>
+  <dimension ref="A1:B687"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27077,6 +27137,26 @@
       </c>
       <c r="B685" t="n">
         <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B686" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="n">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>
@@ -27245,28 +27325,28 @@
         <v>0.1249</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004536236151285322</v>
+        <v>0.001970275157445986</v>
       </c>
       <c r="J2" t="n">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="K2" t="n">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001407645603160868</v>
+        <v>2.655233485437947e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>2.073206663477227</v>
+        <v>2.078445062859418</v>
       </c>
       <c r="N2" t="n">
-        <v>7.887890960631122</v>
+        <v>7.918073614732323</v>
       </c>
       <c r="O2" t="n">
-        <v>2.808538936997513</v>
+        <v>2.813907179480575</v>
       </c>
       <c r="P2" t="n">
-        <v>369.5220739776819</v>
+        <v>369.5488825918152</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -27327,28 +27407,28 @@
         <v>0.0927</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.001687003371275859</v>
+        <v>-0.001618418350708797</v>
       </c>
       <c r="J3" t="n">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="K3" t="n">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="L3" t="n">
-        <v>1.834951447443611e-05</v>
+        <v>1.699916007780189e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.254227749356692</v>
+        <v>2.248514224924202</v>
       </c>
       <c r="N3" t="n">
-        <v>8.369960488666768</v>
+        <v>8.345008090627262</v>
       </c>
       <c r="O3" t="n">
-        <v>2.893088399732502</v>
+        <v>2.888772765488359</v>
       </c>
       <c r="P3" t="n">
-        <v>369.5670509504048</v>
+        <v>369.5663342509013</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -27409,28 +27489,28 @@
         <v>0.0609</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.08860588347029998</v>
+        <v>-0.08839822240382318</v>
       </c>
       <c r="J4" t="n">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="K4" t="n">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05252554375842422</v>
+        <v>0.05261887973097545</v>
       </c>
       <c r="M4" t="n">
-        <v>2.152730979989974</v>
+        <v>2.147145224455107</v>
       </c>
       <c r="N4" t="n">
-        <v>7.642687938204685</v>
+        <v>7.619916494763821</v>
       </c>
       <c r="O4" t="n">
-        <v>2.764541180413973</v>
+        <v>2.760419622949348</v>
       </c>
       <c r="P4" t="n">
-        <v>370.1789114830745</v>
+        <v>370.1767418315683</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -27491,28 +27571,28 @@
         <v>0.0518</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01069544454947816</v>
+        <v>-0.01219954824566263</v>
       </c>
       <c r="J5" t="n">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="K5" t="n">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000950906085795844</v>
+        <v>0.001241355214947504</v>
       </c>
       <c r="M5" t="n">
-        <v>2.071678225023719</v>
+        <v>2.072470937623812</v>
       </c>
       <c r="N5" t="n">
-        <v>6.485910294699033</v>
+        <v>6.48532875379342</v>
       </c>
       <c r="O5" t="n">
-        <v>2.546745039201811</v>
+        <v>2.546630863276698</v>
       </c>
       <c r="P5" t="n">
-        <v>368.2208339748666</v>
+        <v>368.2365484363124</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -27573,28 +27653,28 @@
         <v>0.0673</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04909973656381671</v>
+        <v>0.0482435762624477</v>
       </c>
       <c r="J6" t="n">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="K6" t="n">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0231882422574603</v>
+        <v>0.02252583952155807</v>
       </c>
       <c r="M6" t="n">
-        <v>1.849946640037527</v>
+        <v>1.847441180201223</v>
       </c>
       <c r="N6" t="n">
-        <v>5.480566187222735</v>
+        <v>5.469949395440179</v>
       </c>
       <c r="O6" t="n">
-        <v>2.34106091061782</v>
+        <v>2.338792294206602</v>
       </c>
       <c r="P6" t="n">
-        <v>369.1915416584025</v>
+        <v>369.2004866602146</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -27655,28 +27735,28 @@
         <v>0.0747</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07147845406845801</v>
+        <v>0.07083224607101481</v>
       </c>
       <c r="J7" t="n">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="K7" t="n">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04034595313031741</v>
+        <v>0.03987968595706481</v>
       </c>
       <c r="M7" t="n">
-        <v>2.014034212751147</v>
+        <v>2.010998002101666</v>
       </c>
       <c r="N7" t="n">
-        <v>6.558266716811588</v>
+        <v>6.542081884454854</v>
       </c>
       <c r="O7" t="n">
-        <v>2.560911305924434</v>
+        <v>2.557749378741955</v>
       </c>
       <c r="P7" t="n">
-        <v>371.5546969631114</v>
+        <v>371.5614483238782</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -27718,7 +27798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H659"/>
+  <dimension ref="A1:H661"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55399,6 +55479,90 @@
         </is>
       </c>
     </row>
+    <row r="660">
+      <c r="A660" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>-36.67136729431186,174.74741964013208</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>-36.67207344671705,174.7473247852052</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>-36.672781136640005,174.7473013145517</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>-36.673490534734256,174.74741158833214</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>-36.67418760982342,174.747622764114</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>-36.67487489213091,174.74787997560142</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>-36.671368221787326,174.74742738638074</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>-36.67207390370502,174.74733259604875</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>-36.67278096163835,174.74730376627068</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>-36.673489024021805,174.74742148128726</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>-36.67418736051896,174.74762407051946</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>-36.674873452023725,174.74788656204126</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0149/nzd0149.xlsx
+++ b/data/nzd0149/nzd0149.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H661"/>
+  <dimension ref="A1:H663"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20268,6 +20268,66 @@
         <v>372.67</v>
       </c>
       <c r="H661" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B662" t="n">
+        <v>367.45</v>
+      </c>
+      <c r="C662" t="n">
+        <v>368.07</v>
+      </c>
+      <c r="D662" t="n">
+        <v>364.32</v>
+      </c>
+      <c r="E662" t="n">
+        <v>364.92</v>
+      </c>
+      <c r="F662" t="n">
+        <v>368.54</v>
+      </c>
+      <c r="G662" t="n">
+        <v>371.1</v>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B663" t="n">
+        <v>367.62</v>
+      </c>
+      <c r="C663" t="n">
+        <v>368.41</v>
+      </c>
+      <c r="D663" t="n">
+        <v>364.89</v>
+      </c>
+      <c r="E663" t="n">
+        <v>365.76</v>
+      </c>
+      <c r="F663" t="n">
+        <v>368.78</v>
+      </c>
+      <c r="G663" t="n">
+        <v>371.68</v>
+      </c>
+      <c r="H663" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -20284,7 +20344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B687"/>
+  <dimension ref="A1:B689"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27157,6 +27217,26 @@
       </c>
       <c r="B687" t="n">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B689" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -27325,28 +27405,28 @@
         <v>0.1249</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001970275157445986</v>
+        <v>0.0007212253748289717</v>
       </c>
       <c r="J2" t="n">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="K2" t="n">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="L2" t="n">
-        <v>2.655233485437947e-05</v>
+        <v>3.575835726965515e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>2.078445062859418</v>
+        <v>2.077808150626716</v>
       </c>
       <c r="N2" t="n">
-        <v>7.918073614732323</v>
+        <v>7.90692529656527</v>
       </c>
       <c r="O2" t="n">
-        <v>2.813907179480575</v>
+        <v>2.811925549612804</v>
       </c>
       <c r="P2" t="n">
-        <v>369.5488825918152</v>
+        <v>369.5619767994997</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -27407,28 +27487,28 @@
         <v>0.0927</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.001618418350708797</v>
+        <v>-0.002394005787906636</v>
       </c>
       <c r="J3" t="n">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="K3" t="n">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="L3" t="n">
-        <v>1.699916007780189e-05</v>
+        <v>3.742011269736167e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.248514224924202</v>
+        <v>2.24494347961997</v>
       </c>
       <c r="N3" t="n">
-        <v>8.345008090627262</v>
+        <v>8.324799855234911</v>
       </c>
       <c r="O3" t="n">
-        <v>2.888772765488359</v>
+        <v>2.885272925605983</v>
       </c>
       <c r="P3" t="n">
-        <v>369.5663342509013</v>
+        <v>369.574464641379</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -27489,28 +27569,28 @@
         <v>0.0609</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.08839822240382318</v>
+        <v>-0.09035912870488949</v>
       </c>
       <c r="J4" t="n">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="K4" t="n">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05261887973097545</v>
+        <v>0.0549777554500559</v>
       </c>
       <c r="M4" t="n">
-        <v>2.147145224455107</v>
+        <v>2.151295931671646</v>
       </c>
       <c r="N4" t="n">
-        <v>7.619916494763821</v>
+        <v>7.628582493909324</v>
       </c>
       <c r="O4" t="n">
-        <v>2.760419622949348</v>
+        <v>2.761988865638188</v>
       </c>
       <c r="P4" t="n">
-        <v>370.1767418315683</v>
+        <v>370.1972981890312</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -27571,28 +27651,28 @@
         <v>0.0518</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01219954824566263</v>
+        <v>-0.01375813558293353</v>
       </c>
       <c r="J5" t="n">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="K5" t="n">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001241355214947504</v>
+        <v>0.001583763510416558</v>
       </c>
       <c r="M5" t="n">
-        <v>2.072470937623812</v>
+        <v>2.073507991834644</v>
       </c>
       <c r="N5" t="n">
-        <v>6.48532875379342</v>
+        <v>6.486123653937932</v>
       </c>
       <c r="O5" t="n">
-        <v>2.546630863276698</v>
+        <v>2.546786927471148</v>
       </c>
       <c r="P5" t="n">
-        <v>368.2365484363124</v>
+        <v>368.2528866791462</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -27653,28 +27733,28 @@
         <v>0.0673</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0482435762624477</v>
+        <v>0.0471481207635055</v>
       </c>
       <c r="J6" t="n">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="K6" t="n">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02252583952155807</v>
+        <v>0.02163813763990885</v>
       </c>
       <c r="M6" t="n">
-        <v>1.847441180201223</v>
+        <v>1.845956157190381</v>
       </c>
       <c r="N6" t="n">
-        <v>5.469949395440179</v>
+        <v>5.463276263886687</v>
       </c>
       <c r="O6" t="n">
-        <v>2.338792294206602</v>
+        <v>2.337365239727563</v>
       </c>
       <c r="P6" t="n">
-        <v>369.2004866602146</v>
+        <v>369.2119705480928</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -27735,28 +27815,28 @@
         <v>0.0747</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07083224607101481</v>
+        <v>0.0696009501493403</v>
       </c>
       <c r="J7" t="n">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="K7" t="n">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03987968595706481</v>
+        <v>0.03873256500177069</v>
       </c>
       <c r="M7" t="n">
-        <v>2.010998002101666</v>
+        <v>2.010776720601388</v>
       </c>
       <c r="N7" t="n">
-        <v>6.542081884454854</v>
+        <v>6.53496190021696</v>
       </c>
       <c r="O7" t="n">
-        <v>2.557749378741955</v>
+        <v>2.556357154275779</v>
       </c>
       <c r="P7" t="n">
-        <v>371.5614483238782</v>
+        <v>371.5743557898033</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -27798,7 +27878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H661"/>
+  <dimension ref="A1:H663"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55563,6 +55643,90 @@
         </is>
       </c>
     </row>
+    <row r="662">
+      <c r="A662" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>-36.671370460976014,174.74744608803888</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>-36.672072650251074,174.74731117202086</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>-36.6727841275695,174.74725941244373</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>-36.67349068580546,174.7474105990366</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>-36.6741885862658,174.74761764735922</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>-36.67487715852837,174.74786961005623</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>-36.671370686219674,174.74744796927084</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>-36.672072872217164,174.7473149658591</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>-36.672783674158254,174.74726576462524</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>-36.673489275807256,174.74741983246142</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>-36.67418808765695,174.74762026017018</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>-36.67487578924666,174.7478758725732</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0149/nzd0149.xlsx
+++ b/data/nzd0149/nzd0149.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H663"/>
+  <dimension ref="A1:H665"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20330,6 +20330,66 @@
       <c r="H663" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B664" t="n">
+        <v>371.01</v>
+      </c>
+      <c r="C664" t="n">
+        <v>369.37</v>
+      </c>
+      <c r="D664" t="n">
+        <v>366.31</v>
+      </c>
+      <c r="E664" t="n">
+        <v>367</v>
+      </c>
+      <c r="F664" t="n">
+        <v>365.52</v>
+      </c>
+      <c r="G664" t="n">
+        <v>370.96</v>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:05:46+00:00</t>
+        </is>
+      </c>
+      <c r="B665" t="n">
+        <v>370.82</v>
+      </c>
+      <c r="C665" t="n">
+        <v>369.69</v>
+      </c>
+      <c r="D665" t="n">
+        <v>367.04</v>
+      </c>
+      <c r="E665" t="n">
+        <v>367</v>
+      </c>
+      <c r="F665" t="n">
+        <v>365.53</v>
+      </c>
+      <c r="G665" t="n">
+        <v>370.29</v>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -20344,7 +20404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B689"/>
+  <dimension ref="A1:B691"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27237,6 +27297,26 @@
       </c>
       <c r="B689" t="n">
         <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B690" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B691" t="n">
+        <v>0.79</v>
       </c>
     </row>
   </sheetData>
@@ -27405,34 +27485,30 @@
         <v>0.1249</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007212253748289717</v>
+        <v>0.001526928802616099</v>
       </c>
       <c r="J2" t="n">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="K2" t="n">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="L2" t="n">
-        <v>3.575835726965515e-06</v>
+        <v>1.612408241380425e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>2.077808150626716</v>
+        <v>2.07589628863399</v>
       </c>
       <c r="N2" t="n">
-        <v>7.90692529656527</v>
+        <v>7.88842265612886</v>
       </c>
       <c r="O2" t="n">
-        <v>2.811925549612804</v>
+        <v>2.808633592359256</v>
       </c>
       <c r="P2" t="n">
-        <v>369.5619767994997</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>369.5534903900754</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>LINESTRING (174.7433798833966 -36.670883533224675, 174.75357302741543 -36.67210388624761)</t>
@@ -27487,34 +27563,30 @@
         <v>0.0927</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.002394005787906636</v>
+        <v>-0.002384572734228888</v>
       </c>
       <c r="J3" t="n">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="K3" t="n">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="L3" t="n">
-        <v>3.742011269736167e-05</v>
+        <v>3.737418517313351e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.24494347961997</v>
+        <v>2.238671866118471</v>
       </c>
       <c r="N3" t="n">
-        <v>8.324799855234911</v>
+        <v>8.299803146386688</v>
       </c>
       <c r="O3" t="n">
-        <v>2.885272925605983</v>
+        <v>2.880937893531669</v>
       </c>
       <c r="P3" t="n">
-        <v>369.574464641379</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>369.5743647984958</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>LINESTRING (174.74320412887437 -36.67183228763671, 174.75348248875972 -36.67243355349016)</t>
@@ -27569,34 +27641,30 @@
         <v>0.0609</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.09035912870488949</v>
+        <v>-0.09104067829025862</v>
       </c>
       <c r="J4" t="n">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="K4" t="n">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0549777554500559</v>
+        <v>0.05608731966584624</v>
       </c>
       <c r="M4" t="n">
-        <v>2.151295931671646</v>
+        <v>2.14846976309758</v>
       </c>
       <c r="N4" t="n">
-        <v>7.628582493909324</v>
+        <v>7.609790710276147</v>
       </c>
       <c r="O4" t="n">
-        <v>2.761988865638188</v>
+        <v>2.758584910833115</v>
       </c>
       <c r="P4" t="n">
-        <v>370.1972981890312</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>370.2044760374922</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>LINESTRING (174.7431993474114 -36.67307385998442, 174.75346457538606 -36.672341046675136)</t>
@@ -27651,34 +27719,30 @@
         <v>0.0518</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01375813558293353</v>
+        <v>-0.01429664147617494</v>
       </c>
       <c r="J5" t="n">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="K5" t="n">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001583763510416558</v>
+        <v>0.00172076278912181</v>
       </c>
       <c r="M5" t="n">
-        <v>2.073507991834644</v>
+        <v>2.069769239518399</v>
       </c>
       <c r="N5" t="n">
-        <v>6.486123653937932</v>
+        <v>6.468948506215852</v>
       </c>
       <c r="O5" t="n">
-        <v>2.546786927471148</v>
+        <v>2.543412767565629</v>
       </c>
       <c r="P5" t="n">
-        <v>368.2528866791462</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>368.2585589011794</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>LINESTRING (174.7433993009227 -36.6741031623728, 174.7535240643608 -36.67255695665072)</t>
@@ -27733,34 +27797,30 @@
         <v>0.0673</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0471481207635055</v>
+        <v>0.04416230330766907</v>
       </c>
       <c r="J6" t="n">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="K6" t="n">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02163813763990885</v>
+        <v>0.0189126603449461</v>
       </c>
       <c r="M6" t="n">
-        <v>1.845956157190381</v>
+        <v>1.851558495780262</v>
       </c>
       <c r="N6" t="n">
-        <v>5.463276263886687</v>
+        <v>5.519415510957833</v>
       </c>
       <c r="O6" t="n">
-        <v>2.337365239727563</v>
+        <v>2.349343634072681</v>
       </c>
       <c r="P6" t="n">
-        <v>369.2119705480928</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>369.243420958513</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>LINESTRING (174.7436054159618 -36.67495417503091, 174.7536327300541 -36.6730405460974)</t>
@@ -27815,34 +27875,30 @@
         <v>0.0747</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0696009501493403</v>
+        <v>0.06791358472372352</v>
       </c>
       <c r="J7" t="n">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="K7" t="n">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03873256500177069</v>
+        <v>0.03705538278540055</v>
       </c>
       <c r="M7" t="n">
-        <v>2.010776720601388</v>
+        <v>2.012755706122815</v>
       </c>
       <c r="N7" t="n">
-        <v>6.53496190021696</v>
+        <v>6.538798048470684</v>
       </c>
       <c r="O7" t="n">
-        <v>2.556357154275779</v>
+        <v>2.557107359590263</v>
       </c>
       <c r="P7" t="n">
-        <v>371.5743557898033</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>371.5921302790264</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>LINESTRING (174.74386263085148 -36.6757531963199, 174.75380745948317 -36.673578695995644)</t>
@@ -27878,7 +27934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H663"/>
+  <dimension ref="A1:H665"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55727,6 +55783,90 @@
         </is>
       </c>
     </row>
+    <row r="664">
+      <c r="A664" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>-36.671375177837135,174.74748548325098</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>-36.67207349894427,174.74732567787302</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>-36.67278254460597,174.74728158935773</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>-36.67348719438005,174.74743346275454</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>-36.674194860422226,174.74758476948475</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>-36.67487748904459,174.74786809841416</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:05:46+00:00</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>-36.67137492609487,174.74748338069742</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>-36.6720737078531,174.74732924854436</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>-36.672781963919846,174.74728972460733</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>-36.67348719438005,174.74743346275454</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>-36.67419483964689,174.7475848783519</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>-36.67487907080053,174.74786086412695</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0149/nzd0149.xlsx
+++ b/data/nzd0149/nzd0149.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H665"/>
+  <dimension ref="A1:H668"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20388,6 +20388,96 @@
         <v>370.29</v>
       </c>
       <c r="H665" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B666" t="n">
+        <v>372.11</v>
+      </c>
+      <c r="C666" t="n">
+        <v>370.79</v>
+      </c>
+      <c r="D666" t="n">
+        <v>368.42</v>
+      </c>
+      <c r="E666" t="n">
+        <v>367.77</v>
+      </c>
+      <c r="F666" t="n">
+        <v>367.23</v>
+      </c>
+      <c r="G666" t="n">
+        <v>371.12</v>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:11:49+00:00</t>
+        </is>
+      </c>
+      <c r="B667" t="n">
+        <v>371.7</v>
+      </c>
+      <c r="C667" t="n">
+        <v>370.51</v>
+      </c>
+      <c r="D667" t="n">
+        <v>367.87</v>
+      </c>
+      <c r="E667" t="n">
+        <v>367.16</v>
+      </c>
+      <c r="F667" t="n">
+        <v>368.32</v>
+      </c>
+      <c r="G667" t="n">
+        <v>371.99</v>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:57+00:00</t>
+        </is>
+      </c>
+      <c r="B668" t="n">
+        <v>371.8</v>
+      </c>
+      <c r="C668" t="n">
+        <v>371.78</v>
+      </c>
+      <c r="D668" t="n">
+        <v>368.47</v>
+      </c>
+      <c r="E668" t="n">
+        <v>368.1</v>
+      </c>
+      <c r="F668" t="n">
+        <v>368.56</v>
+      </c>
+      <c r="G668" t="n">
+        <v>372.96</v>
+      </c>
+      <c r="H668" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20404,7 +20494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B691"/>
+  <dimension ref="A1:B694"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27317,6 +27407,36 @@
       </c>
       <c r="B691" t="n">
         <v>0.79</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B692" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B693" t="n">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B694" t="n">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>
@@ -27485,28 +27605,28 @@
         <v>0.1249</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001526928802616099</v>
+        <v>0.003578380891665455</v>
       </c>
       <c r="J2" t="n">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="K2" t="n">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="L2" t="n">
-        <v>1.612408241380425e-05</v>
+        <v>8.917342011027785e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>2.07589628863399</v>
+        <v>2.077604043015392</v>
       </c>
       <c r="N2" t="n">
-        <v>7.88842265612886</v>
+        <v>7.876095573164291</v>
       </c>
       <c r="O2" t="n">
-        <v>2.808633592359256</v>
+        <v>2.806438236121417</v>
       </c>
       <c r="P2" t="n">
-        <v>369.5534903900754</v>
+        <v>369.5318201039468</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27563,28 +27683,28 @@
         <v>0.0927</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.002384572734228888</v>
+        <v>-0.001019353699671663</v>
       </c>
       <c r="J3" t="n">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="K3" t="n">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="L3" t="n">
-        <v>3.737418517313351e-05</v>
+        <v>6.888798149806696e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>2.238671866118471</v>
+        <v>2.236446717206483</v>
       </c>
       <c r="N3" t="n">
-        <v>8.299803146386688</v>
+        <v>8.273996901714112</v>
       </c>
       <c r="O3" t="n">
-        <v>2.880937893531669</v>
+        <v>2.876455614417527</v>
       </c>
       <c r="P3" t="n">
-        <v>369.5743647984958</v>
+        <v>369.5599385360134</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27641,28 +27761,28 @@
         <v>0.0609</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.09104067829025862</v>
+        <v>-0.09062217040671711</v>
       </c>
       <c r="J4" t="n">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="K4" t="n">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05608731966584624</v>
+        <v>0.05611895710472958</v>
       </c>
       <c r="M4" t="n">
-        <v>2.14846976309758</v>
+        <v>2.140707474835995</v>
       </c>
       <c r="N4" t="n">
-        <v>7.609790710276147</v>
+        <v>7.576848246250787</v>
       </c>
       <c r="O4" t="n">
-        <v>2.758584910833115</v>
+        <v>2.752607535819589</v>
       </c>
       <c r="P4" t="n">
-        <v>370.2044760374922</v>
+        <v>370.2000550406439</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27719,28 +27839,28 @@
         <v>0.0518</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01429664147617494</v>
+        <v>-0.01447629289392007</v>
       </c>
       <c r="J5" t="n">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="K5" t="n">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00172076278912181</v>
+        <v>0.001781632730865734</v>
       </c>
       <c r="M5" t="n">
-        <v>2.069769239518399</v>
+        <v>2.06196827559353</v>
       </c>
       <c r="N5" t="n">
-        <v>6.468948506215852</v>
+        <v>6.440715193070353</v>
       </c>
       <c r="O5" t="n">
-        <v>2.543412767565629</v>
+        <v>2.537856416953164</v>
       </c>
       <c r="P5" t="n">
-        <v>368.2585589011794</v>
+        <v>368.2604558706489</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27797,28 +27917,28 @@
         <v>0.0673</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04416230330766907</v>
+        <v>0.04202135627761381</v>
       </c>
       <c r="J6" t="n">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="K6" t="n">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0189126603449461</v>
+        <v>0.01724114579187874</v>
       </c>
       <c r="M6" t="n">
-        <v>1.851558495780262</v>
+        <v>1.851267669571312</v>
       </c>
       <c r="N6" t="n">
-        <v>5.519415510957833</v>
+        <v>5.52119352990745</v>
       </c>
       <c r="O6" t="n">
-        <v>2.349343634072681</v>
+        <v>2.349722011197803</v>
       </c>
       <c r="P6" t="n">
-        <v>369.243420958513</v>
+        <v>369.2660319518836</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27875,28 +27995,28 @@
         <v>0.0747</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06791358472372352</v>
+        <v>0.06668161818838751</v>
       </c>
       <c r="J7" t="n">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="K7" t="n">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03705538278540055</v>
+        <v>0.0360587708250919</v>
       </c>
       <c r="M7" t="n">
-        <v>2.012755706122815</v>
+        <v>2.009534628060217</v>
       </c>
       <c r="N7" t="n">
-        <v>6.538798048470684</v>
+        <v>6.520244732011083</v>
       </c>
       <c r="O7" t="n">
-        <v>2.557107359590263</v>
+        <v>2.553476988737334</v>
       </c>
       <c r="P7" t="n">
-        <v>371.5921302790264</v>
+        <v>371.605136746069</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27934,7 +28054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H665"/>
+  <dimension ref="A1:H668"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55867,6 +55987,132 @@
         </is>
       </c>
     </row>
+    <row r="666">
+      <c r="A666" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>-36.671376635291544,174.74749765592975</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>-36.672074425976355,174.74734152272717</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>-36.67278086618288,174.7473051035719</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>-36.673485901880134,174.74744192672648</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>-36.67419130783805,174.74760338576536</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>-36.67487711131176,174.7478698260051</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:11:49+00:00</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>-36.671376092058686,174.74749311884034</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>-36.67207424318146,174.74733839838973</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>-36.67278130368698,174.7472989742745</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>-36.67348692580869,174.747435221502</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>-36.67418904332385,174.74761525228246</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>-36.67487505738909,174.74787921978046</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:57+00:00</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>-36.67137622455452,174.74749422544753</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>-36.672075072286205,174.74735256949188</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>-36.67278082640977,174.74730566078077</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>-36.67348534795141,174.74744555414296</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>-36.67418854471506,174.74761786509345</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>-36.67487276738247,174.74788969329947</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0149/nzd0149.xlsx
+++ b/data/nzd0149/nzd0149.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H668"/>
+  <dimension ref="A1:H675"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20478,6 +20478,216 @@
         <v>372.96</v>
       </c>
       <c r="H668" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B669" t="n">
+        <v>371.41</v>
+      </c>
+      <c r="C669" t="n">
+        <v>371.46</v>
+      </c>
+      <c r="D669" t="n">
+        <v>369.07</v>
+      </c>
+      <c r="E669" t="n">
+        <v>368.12</v>
+      </c>
+      <c r="F669" t="n">
+        <v>368.76</v>
+      </c>
+      <c r="G669" t="n">
+        <v>373.12</v>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B670" t="n">
+        <v>370.58</v>
+      </c>
+      <c r="C670" t="n">
+        <v>370.57</v>
+      </c>
+      <c r="D670" t="n">
+        <v>368.45</v>
+      </c>
+      <c r="E670" t="n">
+        <v>367.64</v>
+      </c>
+      <c r="F670" t="n">
+        <v>368.58</v>
+      </c>
+      <c r="G670" t="n">
+        <v>372.94</v>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B671" t="n">
+        <v>369.6</v>
+      </c>
+      <c r="C671" t="n">
+        <v>369.54</v>
+      </c>
+      <c r="D671" t="n">
+        <v>367.83</v>
+      </c>
+      <c r="E671" t="n">
+        <v>367.15</v>
+      </c>
+      <c r="F671" t="n">
+        <v>368.15</v>
+      </c>
+      <c r="G671" t="n">
+        <v>372.67</v>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B672" t="n">
+        <v>369.29</v>
+      </c>
+      <c r="C672" t="n">
+        <v>368.6</v>
+      </c>
+      <c r="D672" t="n">
+        <v>367.36</v>
+      </c>
+      <c r="E672" t="n">
+        <v>367.26</v>
+      </c>
+      <c r="F672" t="n">
+        <v>368.46</v>
+      </c>
+      <c r="G672" t="n">
+        <v>372.92</v>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B673" t="n">
+        <v>368.76</v>
+      </c>
+      <c r="C673" t="n">
+        <v>367.99</v>
+      </c>
+      <c r="D673" t="n">
+        <v>367.06</v>
+      </c>
+      <c r="E673" t="n">
+        <v>367.28</v>
+      </c>
+      <c r="F673" t="n">
+        <v>368.57</v>
+      </c>
+      <c r="G673" t="n">
+        <v>372.91</v>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B674" t="n">
+        <v>368.93</v>
+      </c>
+      <c r="C674" t="n">
+        <v>367.98</v>
+      </c>
+      <c r="D674" t="n">
+        <v>367.23</v>
+      </c>
+      <c r="E674" t="n">
+        <v>367.88</v>
+      </c>
+      <c r="F674" t="n">
+        <v>368.78</v>
+      </c>
+      <c r="G674" t="n">
+        <v>373.45</v>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:04:56+00:00</t>
+        </is>
+      </c>
+      <c r="B675" t="n">
+        <v>369.4</v>
+      </c>
+      <c r="C675" t="n">
+        <v>368.73</v>
+      </c>
+      <c r="D675" t="n">
+        <v>367.79</v>
+      </c>
+      <c r="E675" t="n">
+        <v>368.14</v>
+      </c>
+      <c r="F675" t="n">
+        <v>369.35</v>
+      </c>
+      <c r="G675" t="n">
+        <v>373.98</v>
+      </c>
+      <c r="H675" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20494,7 +20704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B694"/>
+  <dimension ref="A1:B701"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27437,6 +27647,76 @@
       </c>
       <c r="B694" t="n">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B695" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B696" t="n">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B697" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B698" t="n">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B699" t="n">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B700" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B701" t="n">
+        <v>-0.89</v>
       </c>
     </row>
   </sheetData>
@@ -27605,28 +27885,28 @@
         <v>0.1249</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003578380891665455</v>
+        <v>0.003746992894922551</v>
       </c>
       <c r="J2" t="n">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="K2" t="n">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="L2" t="n">
-        <v>8.917342011027785e-05</v>
+        <v>9.996706482517936e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>2.077604043015392</v>
+        <v>2.063390095184944</v>
       </c>
       <c r="N2" t="n">
-        <v>7.876095573164291</v>
+        <v>7.802479107513009</v>
       </c>
       <c r="O2" t="n">
-        <v>2.806438236121417</v>
+        <v>2.79329180493428</v>
       </c>
       <c r="P2" t="n">
-        <v>369.5318201039468</v>
+        <v>369.5300466018661</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27683,28 +27963,28 @@
         <v>0.0927</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.001019353699671663</v>
+        <v>-0.001571437711927843</v>
       </c>
       <c r="J3" t="n">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="K3" t="n">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="L3" t="n">
-        <v>6.888798149806696e-06</v>
+        <v>1.672256791496185e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.236446717206483</v>
+        <v>2.224367033006925</v>
       </c>
       <c r="N3" t="n">
-        <v>8.273996901714112</v>
+        <v>8.204485370499345</v>
       </c>
       <c r="O3" t="n">
-        <v>2.876455614417527</v>
+        <v>2.864347285246561</v>
       </c>
       <c r="P3" t="n">
-        <v>369.5599385360134</v>
+        <v>369.565839615048</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27761,28 +28041,28 @@
         <v>0.0609</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.09062217040671711</v>
+        <v>-0.0905331310006478</v>
       </c>
       <c r="J4" t="n">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="K4" t="n">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05611895710472958</v>
+        <v>0.05722312004049201</v>
       </c>
       <c r="M4" t="n">
-        <v>2.140707474835995</v>
+        <v>2.123910575421485</v>
       </c>
       <c r="N4" t="n">
-        <v>7.576848246250787</v>
+        <v>7.502736670577987</v>
       </c>
       <c r="O4" t="n">
-        <v>2.752607535819589</v>
+        <v>2.73911238735799</v>
       </c>
       <c r="P4" t="n">
-        <v>370.2000550406439</v>
+        <v>370.1991217633143</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27839,28 +28119,28 @@
         <v>0.0518</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01447629289392007</v>
+        <v>-0.01496357690235352</v>
       </c>
       <c r="J5" t="n">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="K5" t="n">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001781632730865734</v>
+        <v>0.001947364245198591</v>
       </c>
       <c r="M5" t="n">
-        <v>2.06196827559353</v>
+        <v>2.044354154767542</v>
       </c>
       <c r="N5" t="n">
-        <v>6.440715193070353</v>
+        <v>6.375941553791701</v>
       </c>
       <c r="O5" t="n">
-        <v>2.537856416953164</v>
+        <v>2.525062683141094</v>
       </c>
       <c r="P5" t="n">
-        <v>368.2604558706489</v>
+        <v>368.2656374938028</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27917,28 +28197,28 @@
         <v>0.0673</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04202135627761381</v>
+        <v>0.03847226149237313</v>
       </c>
       <c r="J6" t="n">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="K6" t="n">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01724114579187874</v>
+        <v>0.01474534550322237</v>
       </c>
       <c r="M6" t="n">
-        <v>1.851267669571312</v>
+        <v>1.84546599116406</v>
       </c>
       <c r="N6" t="n">
-        <v>5.52119352990745</v>
+        <v>5.494854629993025</v>
       </c>
       <c r="O6" t="n">
-        <v>2.349722011197803</v>
+        <v>2.344110626654174</v>
       </c>
       <c r="P6" t="n">
-        <v>369.2660319518836</v>
+        <v>369.3037749619259</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27995,28 +28275,28 @@
         <v>0.0747</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06668161818838751</v>
+        <v>0.06618063209586267</v>
       </c>
       <c r="J7" t="n">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="K7" t="n">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0360587708250919</v>
+        <v>0.03633049383582565</v>
       </c>
       <c r="M7" t="n">
-        <v>2.009534628060217</v>
+        <v>1.992974332665361</v>
       </c>
       <c r="N7" t="n">
-        <v>6.520244732011083</v>
+        <v>6.454845778953591</v>
       </c>
       <c r="O7" t="n">
-        <v>2.553476988737334</v>
+        <v>2.540638852523827</v>
       </c>
       <c r="P7" t="n">
-        <v>371.605136746069</v>
+        <v>371.6104578948799</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28054,7 +28334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H668"/>
+  <dimension ref="A1:H675"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56113,6 +56393,300 @@
         </is>
       </c>
     </row>
+    <row r="669">
+      <c r="A669" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>-36.67137570782069,174.7474899096796</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>-36.67207486337809,174.74734899882046</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>-36.67278034913219,174.74731234728696</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>-36.67348531437997,174.74744577398639</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>-36.67418812920769,174.74762004243595</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>-36.674872389649344,174.74789142089017</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>-36.67137460810461,174.74748072484033</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>-36.672074282351815,174.7473390678906</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>-36.67278084231902,174.7473054378972</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>-36.673486120094445,174.74744049774424</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>-36.67418850316433,174.74761808282773</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>-36.67487281459913,174.74788947735064</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>-36.6713733096437,174.74746988009065</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>-36.67207360992711,174.74732757479217</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>-36.672781335505455,174.7472985285074</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>-36.6734869425944,174.74743511158027</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>-36.67418939650504,174.74761340154132</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>-36.674873452023725,174.74788656204126</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>-36.67137289890588,174.74746644960865</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>-36.672072996256986,174.74731708594518</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>-36.6727817093723,174.7472932907441</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>-36.673486757951586,174.74743632071915</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>-36.67418875246874,174.7476167764222</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>-36.67487286181576,174.74788926140178</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>-36.67137219667642,174.74746058459118</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>-36.67207259802374,174.74731027935306</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>-36.67278194801063,174.74728994749086</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>-36.67348672438015,174.74743654056257</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>-36.67418852393969,174.7476179739606</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>-36.67487288542408,174.7478891534274</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>-36.67137242191986,174.7474624658232</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>-36.67207259149532,174.74731016776957</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>-36.67278181278225,174.74729184200103</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>-36.673485717237234,174.74744313586532</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>-36.67418808765695,174.74762026017018</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>-36.67487161057468,174.74789498404596</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:04:56+00:00</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>-36.671373044651574,174.74746766687645</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>-36.6720730811263,174.7473185365304</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>-36.672781367323914,174.74729808274031</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>-36.67348528080853,174.74744599382979</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>-36.67418690346073,174.7476264655961</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>-36.67487035933332,174.7479007066899</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0149/nzd0149.xlsx
+++ b/data/nzd0149/nzd0149.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H675"/>
+  <dimension ref="A1:H678"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20688,6 +20688,96 @@
         <v>373.98</v>
       </c>
       <c r="H675" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B676" t="n">
+        <v>368.69</v>
+      </c>
+      <c r="C676" t="n">
+        <v>367.78</v>
+      </c>
+      <c r="D676" t="n">
+        <v>368.07</v>
+      </c>
+      <c r="E676" t="n">
+        <v>367.73</v>
+      </c>
+      <c r="F676" t="n">
+        <v>370.06</v>
+      </c>
+      <c r="G676" t="n">
+        <v>374.07</v>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B677" t="n">
+        <v>369.3</v>
+      </c>
+      <c r="C677" t="n">
+        <v>368.79</v>
+      </c>
+      <c r="D677" t="n">
+        <v>368.72</v>
+      </c>
+      <c r="E677" t="n">
+        <v>368.01</v>
+      </c>
+      <c r="F677" t="n">
+        <v>370.38</v>
+      </c>
+      <c r="G677" t="n">
+        <v>374.36</v>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B678" t="n">
+        <v>369.55</v>
+      </c>
+      <c r="C678" t="n">
+        <v>368.43</v>
+      </c>
+      <c r="D678" t="n">
+        <v>368.32</v>
+      </c>
+      <c r="E678" t="n">
+        <v>367.47</v>
+      </c>
+      <c r="F678" t="n">
+        <v>370.12</v>
+      </c>
+      <c r="G678" t="n">
+        <v>374.15</v>
+      </c>
+      <c r="H678" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20704,7 +20794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B701"/>
+  <dimension ref="A1:B704"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27716,6 +27806,36 @@
         </is>
       </c>
       <c r="B701" t="n">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B702" t="n">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B703" t="n">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B704" t="n">
         <v>-0.89</v>
       </c>
     </row>
@@ -27885,28 +28005,28 @@
         <v>0.1249</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003746992894922551</v>
+        <v>0.003349393880084305</v>
       </c>
       <c r="J2" t="n">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="K2" t="n">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="L2" t="n">
-        <v>9.996706482517936e-05</v>
+        <v>8.065262024437025e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>2.063390095184944</v>
+        <v>2.056024036607427</v>
       </c>
       <c r="N2" t="n">
-        <v>7.802479107513009</v>
+        <v>7.769373219400472</v>
       </c>
       <c r="O2" t="n">
-        <v>2.79329180493428</v>
+        <v>2.787359542542094</v>
       </c>
       <c r="P2" t="n">
-        <v>369.5300466018661</v>
+        <v>369.5342915962409</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27963,28 +28083,28 @@
         <v>0.0927</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.001571437711927843</v>
+        <v>-0.002615996839047519</v>
       </c>
       <c r="J3" t="n">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="K3" t="n">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="L3" t="n">
-        <v>1.672256791496185e-05</v>
+        <v>4.675944563814483e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.224367033006925</v>
+        <v>2.218913380807484</v>
       </c>
       <c r="N3" t="n">
-        <v>8.204485370499345</v>
+        <v>8.175076348800927</v>
       </c>
       <c r="O3" t="n">
-        <v>2.864347285246561</v>
+        <v>2.859209042515242</v>
       </c>
       <c r="P3" t="n">
-        <v>369.565839615048</v>
+        <v>369.5769973038144</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28041,28 +28161,28 @@
         <v>0.0609</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0905331310006478</v>
+        <v>-0.09000918093387494</v>
       </c>
       <c r="J4" t="n">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="K4" t="n">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05722312004049201</v>
+        <v>0.05711374116436219</v>
       </c>
       <c r="M4" t="n">
-        <v>2.123910575421485</v>
+        <v>2.116859483273837</v>
       </c>
       <c r="N4" t="n">
-        <v>7.502736670577987</v>
+        <v>7.471354893093792</v>
       </c>
       <c r="O4" t="n">
-        <v>2.73911238735799</v>
+        <v>2.733377927234687</v>
       </c>
       <c r="P4" t="n">
-        <v>370.1991217633143</v>
+        <v>370.193524843873</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28119,28 +28239,28 @@
         <v>0.0518</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01496357690235352</v>
+        <v>-0.01507659552612206</v>
       </c>
       <c r="J5" t="n">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="K5" t="n">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001947364245198591</v>
+        <v>0.001996230858947401</v>
       </c>
       <c r="M5" t="n">
-        <v>2.044354154767542</v>
+        <v>2.036239615127582</v>
       </c>
       <c r="N5" t="n">
-        <v>6.375941553791701</v>
+        <v>6.347972449173772</v>
       </c>
       <c r="O5" t="n">
-        <v>2.525062683141094</v>
+        <v>2.519518297050802</v>
       </c>
       <c r="P5" t="n">
-        <v>368.2656374938028</v>
+        <v>368.2668463638019</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28197,28 +28317,28 @@
         <v>0.0673</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03847226149237313</v>
+        <v>0.03834275658895758</v>
       </c>
       <c r="J6" t="n">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="K6" t="n">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01474534550322237</v>
+        <v>0.01478976321980352</v>
       </c>
       <c r="M6" t="n">
-        <v>1.84546599116406</v>
+        <v>1.837908495109131</v>
       </c>
       <c r="N6" t="n">
-        <v>5.494854629993025</v>
+        <v>5.47068121832552</v>
       </c>
       <c r="O6" t="n">
-        <v>2.344110626654174</v>
+        <v>2.338948742132995</v>
       </c>
       <c r="P6" t="n">
-        <v>369.3037749619259</v>
+        <v>369.3051587238418</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28275,28 +28395,28 @@
         <v>0.0747</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06618063209586267</v>
+        <v>0.06689150110550739</v>
       </c>
       <c r="J7" t="n">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="K7" t="n">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03633049383582565</v>
+        <v>0.03742224921489279</v>
       </c>
       <c r="M7" t="n">
-        <v>1.992974332665361</v>
+        <v>1.98790636552853</v>
       </c>
       <c r="N7" t="n">
-        <v>6.454845778953591</v>
+        <v>6.429169349367782</v>
       </c>
       <c r="O7" t="n">
-        <v>2.540638852523827</v>
+        <v>2.535580673015115</v>
       </c>
       <c r="P7" t="n">
-        <v>371.6104578948799</v>
+        <v>371.6028642833992</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28334,7 +28454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H675"/>
+  <dimension ref="A1:H678"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56687,6 +56807,132 @@
         </is>
       </c>
     </row>
+    <row r="676">
+      <c r="A676" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>-36.67137210392914,174.74745980996622</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>-36.67207246092696,174.74730793610001</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>-36.67278114459462,174.7473012031099</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>-36.673485969023,174.74744148703965</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>-36.67418542840885,174.74763419516142</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>-36.674870146858346,174.7479016784596</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>-36.671372912155476,174.74746656026937</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>-36.672073120296766,174.74731920603125</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>-36.67278062754415,174.74730844682503</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>-36.67348549902289,174.74744456484754</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>-36.67418476359657,174.7476376789091</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>-36.674869462216705,174.7479048097175</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>-36.67137324339568,174.7474693267871</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>-36.67207288527399,174.74731518902604</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>-36.67278094572911,174.7473039891542</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>-36.67348640545161,174.74743862907513</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>-36.67418530375655,174.7476348483641</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>-36.6748699579917,174.7479025422549</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
